--- a/inasistencias-5a-InstrumentalYsistemasElectricos/alumnos-5a-InstrumentalYsistElectricos.xlsx
+++ b/inasistencias-5a-InstrumentalYsistemasElectricos/alumnos-5a-InstrumentalYsistElectricos.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="120">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -217,8 +217,7 @@
     <t xml:space="preserve">Zarraga (recur)</t>
   </si>
   <si>
-    <t xml:space="preserve">SANTIBAÑEZ RAMÍREZ
-</t>
+    <t xml:space="preserve">SANTIBAÑEZ RAMÍREZ (recur)</t>
   </si>
   <si>
     <t xml:space="preserve">nombres</t>
@@ -236,10 +235,16 @@
     <t xml:space="preserve">1-sistVuelo</t>
   </si>
   <si>
+    <t xml:space="preserve">recup</t>
+  </si>
+  <si>
     <t xml:space="preserve">2-indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">3-cabinas</t>
+    <t xml:space="preserve">Recup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-cabinas</t>
   </si>
   <si>
     <t xml:space="preserve">6-inst de abordo</t>
@@ -251,13 +256,31 @@
     <t xml:space="preserve">valoracion</t>
   </si>
   <si>
+    <t xml:space="preserve">Chaya-DeCarlo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proyecto ADF</t>
+  </si>
+  <si>
     <t xml:space="preserve">Investigacion</t>
   </si>
   <si>
     <t xml:space="preserve">Manrique</t>
   </si>
   <si>
+    <t xml:space="preserve">Gabriel Lautaro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Martinez Ruiz Diaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota : si apruebas teoria y practica = aprueba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">si reprueba una de las partes= Reprueba</t>
   </si>
   <si>
     <t xml:space="preserve">Calificación/10,00</t>
@@ -373,7 +396,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -395,6 +418,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -452,7 +482,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -469,6 +499,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -477,12 +511,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -494,59 +536,47 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="6">
     <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF006600"/>
+        <sz val="12"/>
+      </font>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FFCC0000"/>
+        <sz val="12"/>
+      </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="12"/>
+      </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCC0000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCFFCC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFCCCC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF006600"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -773,9 +803,10 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="35.71"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.79"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="35.71"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="20" min="5" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="8.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="985" min="985" style="1" width="9.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16346" style="1" width="10.58"/>
   </cols>
@@ -854,19 +885,19 @@
         <v>46181</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>46195</v>
+        <v>46209</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>46209</v>
+        <v>46237</v>
       </c>
       <c r="AA2" s="3" t="n">
-        <v>46216</v>
+        <v>46244</v>
       </c>
       <c r="AB2" s="3" t="n">
         <v>46223</v>
@@ -1001,6 +1032,21 @@
       <c r="V3" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="W3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -1062,6 +1108,21 @@
       <c r="V4" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="W4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA4" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -1129,6 +1190,21 @@
       <c r="V5" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="W5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -1188,6 +1264,21 @@
       <c r="V6" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="W6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA6" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -1247,6 +1338,21 @@
       <c r="V7" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="W7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA7" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -1306,6 +1412,21 @@
       <c r="V8" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="W8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA8" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -1365,54 +1486,84 @@
       <c r="V9" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="W9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA9" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="6"/>
+      <c r="C10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="J10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="R10" s="5" t="n">
+      <c r="F10" s="6"/>
+      <c r="J10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="R10" s="6" t="n">
         <f aca="false">COUNTIF(F10:Q10,"P")</f>
         <v>7</v>
       </c>
-      <c r="S10" s="5" t="n">
+      <c r="S10" s="6" t="n">
         <f aca="false">COUNTIF(F10:Q10,"A")</f>
         <v>0</v>
       </c>
-      <c r="T10" s="5" t="n">
+      <c r="T10" s="6" t="n">
         <f aca="false">SUM(R10:S10)</f>
         <v>7</v>
       </c>
-      <c r="U10" s="5" t="n">
+      <c r="U10" s="6" t="n">
         <f aca="false">ROUND(R10*10/T10,0)</f>
         <v>10</v>
       </c>
-      <c r="V10" s="4" t="s">
+      <c r="V10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA10" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1474,6 +1625,21 @@
       <c r="V11" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="W11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA11" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -1533,6 +1699,21 @@
       <c r="V12" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="W12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA12" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
@@ -1592,6 +1773,21 @@
       <c r="V13" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="W13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA13" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -1651,6 +1847,21 @@
       <c r="V14" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="W14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA14" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -1710,6 +1921,21 @@
       </c>
       <c r="V15" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA15" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="AKW15" s="1"/>
       <c r="AKX15" s="1"/>
@@ -1803,7 +2029,7 @@
       <c r="B16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D16" s="2"/>
@@ -1857,54 +2083,84 @@
       <c r="V16" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
+      <c r="W16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA16" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5" t="s">
+      <c r="B17" s="6"/>
+      <c r="C17" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="5"/>
-      <c r="J17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R17" s="5" t="n">
+      <c r="F17" s="6"/>
+      <c r="J17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="R17" s="6" t="n">
         <f aca="false">COUNTIF(F17:Q17,"P")</f>
         <v>6</v>
       </c>
-      <c r="S17" s="5" t="n">
+      <c r="S17" s="6" t="n">
         <f aca="false">COUNTIF(F17:Q17,"A")</f>
         <v>1</v>
       </c>
-      <c r="T17" s="5" t="n">
+      <c r="T17" s="6" t="n">
         <f aca="false">SUM(R17:S17)</f>
         <v>7</v>
       </c>
-      <c r="U17" s="5" t="n">
+      <c r="U17" s="6" t="n">
         <f aca="false">ROUND(R17*10/T17,0)</f>
         <v>9</v>
       </c>
-      <c r="V17" s="4" t="s">
+      <c r="V17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="W17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="X17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA17" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1966,6 +2222,21 @@
       </c>
       <c r="V18" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA18" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="AKW18" s="1"/>
       <c r="AKX18" s="1"/>
@@ -2052,143 +2323,158 @@
       <c r="XFC18" s="1"/>
       <c r="XFD18" s="1"/>
     </row>
-    <row r="19" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
+    <row r="19" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="N19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="O19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R19" s="5" t="n">
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="R19" s="6" t="n">
         <f aca="false">COUNTIF(F19:Q19,"P")</f>
         <v>5</v>
       </c>
-      <c r="S19" s="5" t="n">
+      <c r="S19" s="6" t="n">
         <f aca="false">COUNTIF(F19:Q19,"A")</f>
         <v>2</v>
       </c>
-      <c r="T19" s="5" t="n">
+      <c r="T19" s="6" t="n">
         <f aca="false">SUM(R19:S19)</f>
         <v>7</v>
       </c>
-      <c r="U19" s="5" t="n">
+      <c r="U19" s="6" t="n">
         <f aca="false">ROUND(R19*10/T19,0)</f>
         <v>7</v>
       </c>
-      <c r="V19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AKW19" s="4"/>
-      <c r="AKX19" s="4"/>
-      <c r="AKY19" s="4"/>
-      <c r="AKZ19" s="4"/>
-      <c r="ALA19" s="4"/>
-      <c r="ALB19" s="4"/>
-      <c r="ALC19" s="4"/>
-      <c r="ALD19" s="4"/>
-      <c r="ALE19" s="4"/>
-      <c r="ALF19" s="4"/>
-      <c r="ALG19" s="4"/>
-      <c r="ALH19" s="4"/>
-      <c r="ALI19" s="4"/>
-      <c r="ALJ19" s="4"/>
-      <c r="ALK19" s="4"/>
-      <c r="ALL19" s="4"/>
-      <c r="ALM19" s="4"/>
-      <c r="ALN19" s="4"/>
-      <c r="ALO19" s="4"/>
-      <c r="ALP19" s="4"/>
-      <c r="ALQ19" s="4"/>
-      <c r="ALR19" s="4"/>
-      <c r="ALS19" s="4"/>
-      <c r="ALT19" s="4"/>
-      <c r="ALU19" s="4"/>
-      <c r="ALV19" s="4"/>
-      <c r="ALW19" s="4"/>
-      <c r="ALX19" s="4"/>
-      <c r="ALY19" s="4"/>
-      <c r="ALZ19" s="4"/>
-      <c r="AMA19" s="4"/>
-      <c r="AMB19" s="4"/>
-      <c r="AMC19" s="4"/>
-      <c r="AMD19" s="4"/>
-      <c r="AME19" s="4"/>
-      <c r="AMF19" s="4"/>
-      <c r="AMG19" s="4"/>
-      <c r="AMH19" s="4"/>
-      <c r="AMI19" s="4"/>
-      <c r="AMJ19" s="4"/>
-      <c r="AMK19" s="4"/>
-      <c r="AML19" s="4"/>
-      <c r="AMM19" s="4"/>
-      <c r="AMN19" s="4"/>
-      <c r="AMO19" s="4"/>
-      <c r="XDR19" s="4"/>
-      <c r="XDS19" s="4"/>
-      <c r="XDT19" s="4"/>
-      <c r="XDU19" s="4"/>
-      <c r="XDV19" s="4"/>
-      <c r="XDW19" s="4"/>
-      <c r="XDX19" s="4"/>
-      <c r="XDY19" s="4"/>
-      <c r="XDZ19" s="4"/>
-      <c r="XEA19" s="4"/>
-      <c r="XEB19" s="4"/>
-      <c r="XEC19" s="4"/>
-      <c r="XED19" s="4"/>
-      <c r="XEE19" s="4"/>
-      <c r="XEF19" s="4"/>
-      <c r="XEG19" s="4"/>
-      <c r="XEH19" s="4"/>
-      <c r="XEI19" s="4"/>
-      <c r="XEJ19" s="4"/>
-      <c r="XEK19" s="4"/>
-      <c r="XEL19" s="4"/>
-      <c r="XEM19" s="4"/>
-      <c r="XEN19" s="4"/>
-      <c r="XEO19" s="4"/>
-      <c r="XEP19" s="4"/>
-      <c r="XEQ19" s="4"/>
-      <c r="XER19" s="4"/>
-      <c r="XES19" s="4"/>
-      <c r="XET19" s="4"/>
-      <c r="XEU19" s="4"/>
-      <c r="XEV19" s="4"/>
-      <c r="XEW19" s="4"/>
-      <c r="XEX19" s="4"/>
-      <c r="XEY19" s="4"/>
-      <c r="XEZ19" s="4"/>
-      <c r="XFA19" s="4"/>
-      <c r="XFB19" s="4"/>
-      <c r="XFC19" s="4"/>
-      <c r="XFD19" s="4"/>
+      <c r="V19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="W19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="X19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AKW19" s="5"/>
+      <c r="AKX19" s="5"/>
+      <c r="AKY19" s="5"/>
+      <c r="AKZ19" s="5"/>
+      <c r="ALA19" s="5"/>
+      <c r="ALB19" s="5"/>
+      <c r="ALC19" s="5"/>
+      <c r="ALD19" s="5"/>
+      <c r="ALE19" s="5"/>
+      <c r="ALF19" s="5"/>
+      <c r="ALG19" s="5"/>
+      <c r="ALH19" s="5"/>
+      <c r="ALI19" s="5"/>
+      <c r="ALJ19" s="5"/>
+      <c r="ALK19" s="5"/>
+      <c r="ALL19" s="5"/>
+      <c r="ALM19" s="5"/>
+      <c r="ALN19" s="5"/>
+      <c r="ALO19" s="5"/>
+      <c r="ALP19" s="5"/>
+      <c r="ALQ19" s="5"/>
+      <c r="ALR19" s="5"/>
+      <c r="ALS19" s="5"/>
+      <c r="ALT19" s="5"/>
+      <c r="ALU19" s="5"/>
+      <c r="ALV19" s="5"/>
+      <c r="ALW19" s="5"/>
+      <c r="ALX19" s="5"/>
+      <c r="ALY19" s="5"/>
+      <c r="ALZ19" s="5"/>
+      <c r="AMA19" s="5"/>
+      <c r="AMB19" s="5"/>
+      <c r="AMC19" s="5"/>
+      <c r="AMD19" s="5"/>
+      <c r="AME19" s="5"/>
+      <c r="AMF19" s="5"/>
+      <c r="AMG19" s="5"/>
+      <c r="AMH19" s="5"/>
+      <c r="AMI19" s="5"/>
+      <c r="AMJ19" s="5"/>
+      <c r="AMK19" s="5"/>
+      <c r="AML19" s="5"/>
+      <c r="AMM19" s="5"/>
+      <c r="AMN19" s="5"/>
+      <c r="AMO19" s="5"/>
+      <c r="XDR19" s="5"/>
+      <c r="XDS19" s="5"/>
+      <c r="XDT19" s="5"/>
+      <c r="XDU19" s="5"/>
+      <c r="XDV19" s="5"/>
+      <c r="XDW19" s="5"/>
+      <c r="XDX19" s="5"/>
+      <c r="XDY19" s="5"/>
+      <c r="XDZ19" s="5"/>
+      <c r="XEA19" s="5"/>
+      <c r="XEB19" s="5"/>
+      <c r="XEC19" s="5"/>
+      <c r="XED19" s="5"/>
+      <c r="XEE19" s="5"/>
+      <c r="XEF19" s="5"/>
+      <c r="XEG19" s="5"/>
+      <c r="XEH19" s="5"/>
+      <c r="XEI19" s="5"/>
+      <c r="XEJ19" s="5"/>
+      <c r="XEK19" s="5"/>
+      <c r="XEL19" s="5"/>
+      <c r="XEM19" s="5"/>
+      <c r="XEN19" s="5"/>
+      <c r="XEO19" s="5"/>
+      <c r="XEP19" s="5"/>
+      <c r="XEQ19" s="5"/>
+      <c r="XER19" s="5"/>
+      <c r="XES19" s="5"/>
+      <c r="XET19" s="5"/>
+      <c r="XEU19" s="5"/>
+      <c r="XEV19" s="5"/>
+      <c r="XEW19" s="5"/>
+      <c r="XEX19" s="5"/>
+      <c r="XEY19" s="5"/>
+      <c r="XEZ19" s="5"/>
+      <c r="XFA19" s="5"/>
+      <c r="XFB19" s="5"/>
+      <c r="XFC19" s="5"/>
+      <c r="XFD19" s="5"/>
     </row>
     <row r="20" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
@@ -2248,6 +2534,21 @@
       <c r="V20" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="W20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA20" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -2310,6 +2611,21 @@
       <c r="V21" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="W21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA21" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
@@ -2372,6 +2688,21 @@
       <c r="V22" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="W22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA22" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
@@ -2388,11 +2719,9 @@
       <c r="F23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="1"/>
       <c r="H23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
         <v>13</v>
       </c>
@@ -2411,7 +2740,6 @@
       <c r="O23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P23" s="1"/>
       <c r="Q23" s="1" t="s">
         <v>12</v>
       </c>
@@ -2433,6 +2761,21 @@
       </c>
       <c r="V23" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA23" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2493,6 +2836,21 @@
       </c>
       <c r="V24" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA24" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="AKW24" s="1"/>
       <c r="AKX24" s="1"/>
@@ -2637,6 +2995,21 @@
       <c r="V25" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="W25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA25" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
@@ -2696,6 +3069,21 @@
       <c r="V26" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="W26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA26" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
@@ -2758,6 +3146,21 @@
       <c r="V27" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="W27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA27" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
@@ -2812,77 +3215,139 @@
         <f aca="false">ROUND(R28*10/T28,0)</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="29" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
+      <c r="W28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA28" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="6" t="n">
         <f aca="false">COUNTIF(F3:F25,"p")</f>
         <v>19</v>
       </c>
-      <c r="J29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="N29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="O29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="R29" s="5" t="n">
+      <c r="J29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="O29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="R29" s="6" t="n">
         <f aca="false">COUNTIF(F29:Q29,"P")</f>
         <v>7</v>
       </c>
-      <c r="S29" s="5" t="n">
+      <c r="S29" s="6" t="n">
         <f aca="false">COUNTIF(F29:Q29,"A")</f>
         <v>0</v>
       </c>
-      <c r="T29" s="5" t="n">
+      <c r="T29" s="6" t="n">
         <f aca="false">SUM(R29:S29)</f>
         <v>7</v>
       </c>
-      <c r="U29" s="5" t="n">
+      <c r="U29" s="6" t="n">
         <f aca="false">ROUND(R29*10/T29,0)</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
+      <c r="W29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="X29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA29" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" s="5" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="n">
         <v>28</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="Q30" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
-      <c r="T30" s="2"/>
-      <c r="U30" s="2"/>
+      <c r="F30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q30" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="R30" s="6"/>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
+      <c r="U30" s="6"/>
+      <c r="W30" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="X30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA30" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J31" s="2" t="n">
@@ -2917,6 +3382,26 @@
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
+      <c r="W31" s="2" t="n">
+        <f aca="false">COUNTIF(W3:W30,"P")</f>
+        <v>27</v>
+      </c>
+      <c r="X31" s="2" t="n">
+        <f aca="false">COUNTIF(X3:X30,"P")</f>
+        <v>24</v>
+      </c>
+      <c r="Y31" s="2" t="n">
+        <f aca="false">COUNTIF(Y3:Y30,"P")</f>
+        <v>26</v>
+      </c>
+      <c r="Z31" s="2" t="n">
+        <f aca="false">COUNTIF(Z3:Z30,"P")</f>
+        <v>22</v>
+      </c>
+      <c r="AA31" s="2" t="n">
+        <f aca="false">COUNTIF(AA3:AA30,"P")</f>
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2934,13 +3419,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr defaultColWidth="9.6640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16334" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.82"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="4" style="1" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.97"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="9.66"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="17" min="17" style="1" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16342" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2960,31 +3449,57 @@
         <v>66</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="L2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="8" t="n">
+        <v>46209</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>74</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3000,31 +3515,45 @@
       <c r="D3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="F3" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="1" t="n">
         <v>6.25</v>
       </c>
-      <c r="K3" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D3,E3,F3,G3,H3,I3,J3),0)</f>
-        <v>7</v>
-      </c>
-      <c r="L3" s="1" t="str">
-        <f aca="false">IF(K3&gt;6,"TEA",IF(K3&gt;3,"TEP","TED"))</f>
+      <c r="P3" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D3,F3,G3,I3,K3,M3,O3),0)</f>
+        <v>7</v>
+      </c>
+      <c r="Q3" s="1" t="str">
+        <f aca="false">IF(P3&gt;6,"TEA",IF(P3&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <f aca="false">IF(AND(P3&gt;6,R3&gt;6),ROUND((P3+R3)/2,0),MIN(P3,R3))</f>
+        <v>5</v>
+      </c>
+      <c r="T3" s="1" t="str">
+        <f aca="false">IF(S3&gt;6,"TEA",IF(S3&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3040,31 +3569,45 @@
       <c r="D4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="F4" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="I4" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K4" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D4,E4,F4,G4,H4,I4,J4),0)</f>
-        <v>8</v>
-      </c>
-      <c r="L4" s="1" t="str">
-        <f aca="false">IF(K4&gt;6,"TEA",IF(K4&gt;3,"TEP","TED"))</f>
+        <v>9</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D4,F4,G4,I4,K4,M4,O4),0)</f>
+        <v>8</v>
+      </c>
+      <c r="Q4" s="1" t="str">
+        <f aca="false">IF(P4&gt;6,"TEA",IF(P4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <f aca="false">IF(AND(P4&gt;6,R4&gt;6),ROUND((P4+R4)/2,0),MIN(P4,R4))</f>
+        <v>2</v>
+      </c>
+      <c r="T4" s="1" t="str">
+        <f aca="false">IF(S4&gt;6,"TEA",IF(S4&gt;3,"TEP","TED"))</f>
+        <v>TED</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3078,33 +3621,50 @@
         <v>17</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="G5" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1" t="n">
+      <c r="M5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D5,E5,F5,G5,H5,I5,J5),0)</f>
-        <v>3</v>
-      </c>
-      <c r="L5" s="1" t="str">
-        <f aca="false">IF(K5&gt;6,"TEA",IF(K5&gt;3,"TEP","TED"))</f>
+      <c r="P5" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D5,F5,G5,I5,K5,M5,O5),0)</f>
+        <v>4</v>
+      </c>
+      <c r="Q5" s="1" t="str">
+        <f aca="false">IF(P5&gt;6,"TEA",IF(P5&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <f aca="false">IF(AND(P5&gt;6,R5&gt;6),ROUND((P5+R5)/2,0),MIN(P5,R5))</f>
+        <v>2</v>
+      </c>
+      <c r="T5" s="1" t="str">
+        <f aca="false">IF(S5&gt;6,"TEA",IF(S5&gt;3,"TEP","TED"))</f>
         <v>TED</v>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3120,31 +3680,45 @@
       <c r="D6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="F6" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1" t="n">
+      <c r="I6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1" t="n">
+      <c r="M6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1" t="n">
         <v>4.25</v>
       </c>
-      <c r="K6" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D6,E6,F6,G6,H6,I6,J6),0)</f>
+      <c r="P6" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D6,F6,G6,I6,K6,M6,O6),0)</f>
         <v>4</v>
       </c>
-      <c r="L6" s="1" t="str">
-        <f aca="false">IF(K6&gt;6,"TEA",IF(K6&gt;3,"TEP","TED"))</f>
+      <c r="Q6" s="1" t="str">
+        <f aca="false">IF(P6&gt;6,"TEA",IF(P6&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <f aca="false">IF(AND(P6&gt;6,R6&gt;6),ROUND((P6+R6)/2,0),MIN(P6,R6))</f>
+        <v>4</v>
+      </c>
+      <c r="T6" s="1" t="str">
+        <f aca="false">IF(S6&gt;6,"TEA",IF(S6&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="U6" s="1" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3158,33 +3732,50 @@
         <v>23</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>46209</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1" t="n">
         <v>8</v>
       </c>
       <c r="I7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="K7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1" t="n">
         <v>7.75</v>
       </c>
-      <c r="K7" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D7,E7,F7,G7,H7,I7,J6),0)</f>
-        <v>5</v>
-      </c>
-      <c r="L7" s="1" t="str">
-        <f aca="false">IF(K7&gt;6,"TEA",IF(K7&gt;3,"TEP","TED"))</f>
+      <c r="P7" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D7,F7,G7,I7,K7,M7,O6),0)</f>
+        <v>6</v>
+      </c>
+      <c r="Q7" s="1" t="str">
+        <f aca="false">IF(P7&gt;6,"TEA",IF(P7&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <f aca="false">IF(AND(P7&gt;6,R7&gt;6),ROUND((P7+R7)/2,0),MIN(P7,R7))</f>
+        <v>4</v>
+      </c>
+      <c r="T7" s="1" t="str">
+        <f aca="false">IF(S7&gt;6,"TEA",IF(S7&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3200,31 +3791,45 @@
       <c r="D8" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="F8" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K8" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D8,E8,F8,G8,H8,I8,J7),0)</f>
-        <v>8</v>
-      </c>
-      <c r="L8" s="1" t="str">
-        <f aca="false">IF(K8&gt;6,"TEA",IF(K8&gt;3,"TEP","TED"))</f>
+        <v>7</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D8,F8,G8,I8,K8,M8,O7),0)</f>
+        <v>8</v>
+      </c>
+      <c r="Q8" s="1" t="str">
+        <f aca="false">IF(P8&gt;6,"TEA",IF(P8&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <f aca="false">IF(AND(P8&gt;6,R8&gt;6),ROUND((P8+R8)/2,0),MIN(P8,R8))</f>
+        <v>8</v>
+      </c>
+      <c r="T8" s="1" t="str">
+        <f aca="false">IF(S8&gt;6,"TEA",IF(S8&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="U8" s="1" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3240,855 +3845,1290 @@
       <c r="D9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="F9" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="1" t="n">
+      <c r="K9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1" t="n">
         <v>6.5</v>
       </c>
-      <c r="K9" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D9,E9,F9,G9,H9,I9,J8),0)</f>
-        <v>7</v>
-      </c>
-      <c r="L9" s="1" t="str">
-        <f aca="false">IF(K9&gt;6,"TEA",IF(K9&gt;3,"TEP","TED"))</f>
+      <c r="P9" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D9,F9,G9,I9,K9,M9,O8),0)</f>
+        <v>7</v>
+      </c>
+      <c r="Q9" s="1" t="str">
+        <f aca="false">IF(P9&gt;6,"TEA",IF(P9&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <f aca="false">IF(AND(P9&gt;6,R9&gt;6),ROUND((P9+R9)/2,0),MIN(P9,R9))</f>
+        <v>0</v>
+      </c>
+      <c r="T9" s="1" t="str">
+        <f aca="false">IF(S9&gt;6,"TEA",IF(S9&gt;3,"TEP","TED"))</f>
+        <v>TED</v>
+      </c>
+      <c r="U9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="1" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D10,F10,G10,I10,K10,M10,O9),0)</f>
+        <v>7</v>
+      </c>
+      <c r="Q10" s="1" t="str">
+        <f aca="false">IF(P10&gt;6,"TEA",IF(P10&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <f aca="false">IF(AND(P10&gt;6,R10&gt;6),ROUND((P10+R10)/2,0),MIN(P10,R10))</f>
+        <v>7</v>
+      </c>
+      <c r="T10" s="1" t="str">
+        <f aca="false">IF(S10&gt;6,"TEA",IF(S10&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D10,E10,F10,G10,H10,I10,J9),0)</f>
-        <v>8</v>
-      </c>
-      <c r="L10" s="1" t="str">
-        <f aca="false">IF(K10&gt;6,"TEA",IF(K10&gt;3,"TEP","TED"))</f>
-        <v>TEA</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D11,F11,G11,I11,K11,M11,O10),0)</f>
+        <v>8</v>
+      </c>
+      <c r="Q11" s="1" t="str">
+        <f aca="false">IF(P11&gt;6,"TEA",IF(P11&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <f aca="false">IF(AND(P11&gt;6,R11&gt;6),ROUND((P11+R11)/2,0),MIN(P11,R11))</f>
+        <v>8</v>
+      </c>
+      <c r="T11" s="1" t="str">
+        <f aca="false">IF(S11&gt;6,"TEA",IF(S11&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="U11" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D11,E11,F11,G11,H11,I11,J10),0)</f>
-        <v>4</v>
-      </c>
-      <c r="L11" s="1" t="str">
-        <f aca="false">IF(K11&gt;6,"TEA",IF(K11&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+      <c r="V11" s="1" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="1" t="n">
-        <v>5.5</v>
-      </c>
       <c r="K12" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D12,E12,F12,G12,H12,I12,J11),0)</f>
         <v>4</v>
       </c>
-      <c r="L12" s="1" t="str">
-        <f aca="false">IF(K12&gt;6,"TEA",IF(K12&gt;3,"TEP","TED"))</f>
+      <c r="M12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D12,F12,G12,I12,K12,M12,O11),0)</f>
+        <v>4</v>
+      </c>
+      <c r="Q12" s="1" t="str">
+        <f aca="false">IF(P12&gt;6,"TEA",IF(P12&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <f aca="false">IF(AND(P12&gt;6,R12&gt;6),ROUND((P12+R12)/2,0),MIN(P12,R12))</f>
+        <v>2</v>
+      </c>
+      <c r="T12" s="1" t="str">
+        <f aca="false">IF(S12&gt;6,"TEA",IF(S12&gt;3,"TEP","TED"))</f>
+        <v>TED</v>
+      </c>
+      <c r="U12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="I13" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K13" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D13,E13,F13,G13,H13,I13,J12),0)</f>
-        <v>7</v>
-      </c>
-      <c r="L13" s="1" t="str">
-        <f aca="false">IF(K13&gt;6,"TEA",IF(K13&gt;3,"TEP","TED"))</f>
-        <v>TEA</v>
+        <v>8</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D13,F13,G13,I13,K13,M13,O12),0)</f>
+        <v>4</v>
+      </c>
+      <c r="Q13" s="1" t="str">
+        <f aca="false">IF(P13&gt;6,"TEA",IF(P13&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <f aca="false">IF(AND(P13&gt;6,R13&gt;6),ROUND((P13+R13)/2,0),MIN(P13,R13))</f>
+        <v>2</v>
+      </c>
+      <c r="T13" s="1" t="str">
+        <f aca="false">IF(S13&gt;6,"TEA",IF(S13&gt;3,"TEP","TED"))</f>
+        <v>TED</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>46209</v>
       </c>
       <c r="K14" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D14,E14,F14,G14,H14,I14,J13),0)</f>
-        <v>7</v>
-      </c>
-      <c r="L14" s="1" t="str">
-        <f aca="false">IF(K14&gt;6,"TEA",IF(K14&gt;3,"TEP","TED"))</f>
+        <v>9</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D14,F14,G14,I14,K14,M14,O13),0)</f>
+        <v>8</v>
+      </c>
+      <c r="Q14" s="1" t="str">
+        <f aca="false">IF(P14&gt;6,"TEA",IF(P14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <f aca="false">IF(AND(P14&gt;6,R14&gt;6),ROUND((P14+R14)/2,0),MIN(P14,R14))</f>
+        <v>5</v>
+      </c>
+      <c r="T14" s="1" t="str">
+        <f aca="false">IF(S14&gt;6,"TEA",IF(S14&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>46209</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="1" t="n">
-        <v>6.75</v>
+        <v>6</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>46209</v>
       </c>
       <c r="K15" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D15,E15,F15,G15,H15,I15,J14),0)</f>
-        <v>7</v>
-      </c>
-      <c r="L15" s="1" t="str">
-        <f aca="false">IF(K15&gt;6,"TEA",IF(K15&gt;3,"TEP","TED"))</f>
+        <v>9</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D15,F15,G15,I15,K15,M15,O14),0)</f>
+        <v>8</v>
+      </c>
+      <c r="Q15" s="1" t="str">
+        <f aca="false">IF(P15&gt;6,"TEA",IF(P15&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R15" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <f aca="false">IF(AND(P15&gt;6,R15&gt;6),ROUND((P15+R15)/2,0),MIN(P15,R15))</f>
+        <v>8</v>
+      </c>
+      <c r="T15" s="1" t="str">
+        <f aca="false">IF(S15&gt;6,"TEA",IF(S15&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="F16" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="K16" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D16,E16,F16,G16,H16,I16,J15),0)</f>
-        <v>5</v>
-      </c>
-      <c r="L16" s="1" t="str">
-        <f aca="false">IF(K16&gt;6,"TEA",IF(K16&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+        <v>8</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D16,F16,G16,I16,K16,M16,O15),0)</f>
+        <v>7</v>
+      </c>
+      <c r="Q16" s="1" t="str">
+        <f aca="false">IF(P16&gt;6,"TEA",IF(P16&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="R16" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <f aca="false">IF(AND(P16&gt;6,R16&gt;6),ROUND((P16+R16)/2,0),MIN(P16,R16))</f>
+        <v>7</v>
+      </c>
+      <c r="T16" s="1" t="str">
+        <f aca="false">IF(S16&gt;6,"TEA",IF(S16&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="1" t="n">
-        <v>5.25</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D17,E17,F17,G17,H17,I17,J16),0)</f>
-        <v>7</v>
-      </c>
-      <c r="L17" s="1" t="str">
-        <f aca="false">IF(K17&gt;6,"TEA",IF(K17&gt;3,"TEP","TED"))</f>
+        <v>8</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D17,F17,G17,I17,K17,M17,O16),0)</f>
+        <v>7</v>
+      </c>
+      <c r="Q17" s="1" t="str">
+        <f aca="false">IF(P17&gt;6,"TEA",IF(P17&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R17" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <f aca="false">IF(AND(P17&gt;6,R17&gt;6),ROUND((P17+R17)/2,0),MIN(P17,R17))</f>
+        <v>4</v>
+      </c>
+      <c r="T17" s="1" t="str">
+        <f aca="false">IF(S17&gt;6,"TEA",IF(S17&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I18" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="K18" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D18,E18,F18,G18,H18,I18,J17),0)</f>
-        <v>7</v>
-      </c>
-      <c r="L18" s="1" t="str">
-        <f aca="false">IF(K18&gt;6,"TEA",IF(K18&gt;3,"TEP","TED"))</f>
-        <v>TEA</v>
+      <c r="M18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D18,F18,G18,I18,K18,M18,O17),0)</f>
+        <v>4</v>
+      </c>
+      <c r="Q18" s="1" t="str">
+        <f aca="false">IF(P18&gt;6,"TEA",IF(P18&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="R18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S18" s="1" t="n">
+        <f aca="false">IF(AND(P18&gt;6,R18&gt;6),ROUND((P18+R18)/2,0),MIN(P18,R18))</f>
+        <v>4</v>
+      </c>
+      <c r="T18" s="1" t="str">
+        <f aca="false">IF(S18&gt;6,"TEA",IF(S18&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>49</v>
+        <v>24</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>46209</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H19" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="I19" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>46209</v>
       </c>
       <c r="K19" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D19,E19,F19,G19,H19,I19,J18),0)</f>
-        <v>8</v>
-      </c>
-      <c r="L19" s="1" t="str">
-        <f aca="false">IF(K19&gt;6,"TEA",IF(K19&gt;3,"TEP","TED"))</f>
+        <v>8</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D19,F19,G19,I19,K19,M19,O18),0)</f>
+        <v>7</v>
+      </c>
+      <c r="Q19" s="1" t="str">
+        <f aca="false">IF(P19&gt;6,"TEA",IF(P19&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R19" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="S19" s="1" t="n">
+        <f aca="false">IF(AND(P19&gt;6,R19&gt;6),ROUND((P19+R19)/2,0),MIN(P19,R19))</f>
+        <v>8</v>
+      </c>
+      <c r="T19" s="1" t="str">
+        <f aca="false">IF(S19&gt;6,"TEA",IF(S19&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="H20" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="1" t="n">
-        <v>8.25</v>
+        <v>7</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>46209</v>
       </c>
       <c r="K20" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D20,E20,F20,G20,H20,I20,J19),0)</f>
-        <v>7</v>
-      </c>
-      <c r="L20" s="1" t="str">
-        <f aca="false">IF(K20&gt;6,"TEA",IF(K20&gt;3,"TEP","TED"))</f>
+        <v>7</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D20,F20,G20,I20,K20,M20,O19),0)</f>
+        <v>7</v>
+      </c>
+      <c r="Q20" s="1" t="str">
+        <f aca="false">IF(P20&gt;6,"TEA",IF(P20&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R20" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <f aca="false">IF(AND(P20&gt;6,R20&gt;6),ROUND((P20+R20)/2,0),MIN(P20,R20))</f>
+        <v>7</v>
+      </c>
+      <c r="T20" s="1" t="str">
+        <f aca="false">IF(S20&gt;6,"TEA",IF(S20&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D21,F21,G21,I21,K21,M21,O20),0)</f>
+        <v>8</v>
+      </c>
+      <c r="Q21" s="1" t="str">
+        <f aca="false">IF(P21&gt;6,"TEA",IF(P21&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="R21" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <f aca="false">IF(AND(P21&gt;6,R21&gt;6),ROUND((P21+R21)/2,0),MIN(P21,R21))</f>
+        <v>9</v>
+      </c>
+      <c r="T21" s="1" t="str">
+        <f aca="false">IF(S21&gt;6,"TEA",IF(S21&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="U21" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="K21" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D21,E21,F21,G21,H21,I21,J20),0)</f>
-        <v>3</v>
-      </c>
-      <c r="L21" s="1" t="str">
-        <f aca="false">IF(K21&gt;6,"TEA",IF(K21&gt;3,"TEP","TED"))</f>
-        <v>TED</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>55</v>
+        <v>17</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>46209</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="1" t="n">
-        <v>6.25</v>
+        <v>9</v>
       </c>
       <c r="K22" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D22,E22,F22,G22,H22,I22,J21),0)</f>
+        <v>9</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D22,F22,G22,I22,K22,M22,O21),0)</f>
+        <v>9</v>
+      </c>
+      <c r="Q22" s="1" t="str">
+        <f aca="false">IF(P22&gt;6,"TEA",IF(P22&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="R22" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S22" s="1" t="n">
+        <f aca="false">IF(AND(P22&gt;6,R22&gt;6),ROUND((P22+R22)/2,0),MIN(P22,R22))</f>
+        <v>10</v>
+      </c>
+      <c r="T22" s="1" t="str">
+        <f aca="false">IF(S22&gt;6,"TEA",IF(S22&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="U22" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="L22" s="1" t="str">
-        <f aca="false">IF(K22&gt;6,"TEA",IF(K22&gt;3,"TEP","TED"))</f>
-        <v>TED</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="I23" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J23" s="1" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="K23" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D23,E23,F23,G23,H23,I23,J22),0)</f>
-        <v>9</v>
-      </c>
-      <c r="L23" s="1" t="str">
-        <f aca="false">IF(K23&gt;6,"TEA",IF(K23&gt;3,"TEP","TED"))</f>
+        <v>7</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D23,F23,G23,I23,K23,M23,O22),0)</f>
+        <v>7</v>
+      </c>
+      <c r="Q23" s="1" t="str">
+        <f aca="false">IF(P23&gt;6,"TEA",IF(P23&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="R23" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <f aca="false">IF(AND(P23&gt;6,R23&gt;6),ROUND((P23+R23)/2,0),MIN(P23,R23))</f>
+        <v>8</v>
+      </c>
+      <c r="T23" s="1" t="str">
+        <f aca="false">IF(S23&gt;6,"TEA",IF(S23&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>46209</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G24" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H24" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J24" s="1" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="K24" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D24,E24,F24,G24,H24,I24,J23),0)</f>
-        <v>8</v>
-      </c>
-      <c r="L24" s="1" t="str">
-        <f aca="false">IF(K24&gt;6,"TEA",IF(K24&gt;3,"TEP","TED"))</f>
-        <v>TEA</v>
+      <c r="L24" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="P24" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D24,F24,G24,I24,K24,M24,O23),0)</f>
+        <v>6</v>
+      </c>
+      <c r="Q24" s="1" t="str">
+        <f aca="false">IF(P24&gt;6,"TEA",IF(P24&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="R24" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="S24" s="1" t="n">
+        <f aca="false">IF(AND(P24&gt;6,R24&gt;6),ROUND((P24+R24)/2,0),MIN(P24,R24))</f>
+        <v>6</v>
+      </c>
+      <c r="T24" s="1" t="str">
+        <f aca="false">IF(S24&gt;6,"TEA",IF(S24&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="U24" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="F25" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="1" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D25,F25,G25,I25,K25,M25,O24),0)</f>
         <v>3</v>
       </c>
-      <c r="H25" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I25" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J25" s="1" t="n">
-        <v>7.375</v>
-      </c>
-      <c r="K25" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D25,E25,F25,G25,H25,I25,J24),0)</f>
-        <v>6</v>
-      </c>
-      <c r="L25" s="1" t="str">
-        <f aca="false">IF(K25&gt;6,"TEA",IF(K25&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+      <c r="Q25" s="1" t="str">
+        <f aca="false">IF(P25&gt;6,"TEA",IF(P25&gt;3,"TEP","TED"))</f>
+        <v>TED</v>
+      </c>
+      <c r="R25" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" s="1" t="n">
+        <f aca="false">IF(AND(P25&gt;6,R25&gt;6),ROUND((P25+R25)/2,0),MIN(P25,R25))</f>
+        <v>2</v>
+      </c>
+      <c r="T25" s="1" t="str">
+        <f aca="false">IF(S25&gt;6,"TEA",IF(S25&gt;3,"TEP","TED"))</f>
+        <v>TED</v>
+      </c>
+      <c r="U25" s="1" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C26" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J26" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K26" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D26,E26,F26,G26,H26,I26,J25),0)</f>
-        <v>6</v>
-      </c>
-      <c r="L26" s="1" t="str">
-        <f aca="false">IF(K26&gt;6,"TEA",IF(K26&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+        <v>8</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P26" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D26,F26,G26,I26,K26,M26,O25),0)</f>
+        <v>9</v>
+      </c>
+      <c r="Q26" s="1" t="str">
+        <f aca="false">IF(P26&gt;6,"TEA",IF(P26&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="R26" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <f aca="false">IF(AND(P26&gt;6,R26&gt;6),ROUND((P26+R26)/2,0),MIN(P26,R26))</f>
+        <v>9</v>
+      </c>
+      <c r="T26" s="1" t="str">
+        <f aca="false">IF(S26&gt;6,"TEA",IF(S26&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="U26" s="1" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="C27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O27" s="1" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D27,F27,G27,I27,K27,M27,O26),0)</f>
+        <v>8</v>
+      </c>
+      <c r="Q27" s="1" t="str">
+        <f aca="false">IF(P27&gt;6,"TEA",IF(P27&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="R27" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="S27" s="1" t="n">
+        <f aca="false">IF(AND(P27&gt;6,R27&gt;6),ROUND((P27+R27)/2,0),MIN(P27,R27))</f>
+        <v>8</v>
+      </c>
+      <c r="T27" s="1" t="str">
+        <f aca="false">IF(S27&gt;6,"TEA",IF(S27&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="U27" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="D27" s="1" t="n">
+      <c r="B28" s="5"/>
+      <c r="C28" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I28" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I27" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" s="1" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K27" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D27,E27,F27,G27,H27,I27,J26),0)</f>
-        <v>6</v>
-      </c>
-      <c r="L27" s="1" t="str">
-        <f aca="false">IF(K27&gt;6,"TEA",IF(K27&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="G28" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I28" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="J28" s="1" t="n">
-        <v>4.75</v>
-      </c>
       <c r="K28" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D28,E28,F28,G28,H28,I28,J27),0)</f>
-        <v>7</v>
-      </c>
-      <c r="L28" s="1" t="str">
-        <f aca="false">IF(K28&gt;6,"TEA",IF(K28&gt;3,"TEP","TED"))</f>
+        <v>8</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O28" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="P28" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D28,F28,G28,I28,K28,M28,O27),0)</f>
+        <v>7</v>
+      </c>
+      <c r="Q28" s="1" t="str">
+        <f aca="false">IF(P28&gt;6,"TEA",IF(P28&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="R28" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <f aca="false">IF(AND(P28&gt;6,R28&gt;6),ROUND((P28+R28)/2,0),MIN(P28,R28))</f>
+        <v>8</v>
+      </c>
+      <c r="T28" s="1" t="str">
+        <f aca="false">IF(S28&gt;6,"TEA",IF(S28&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O29" s="1" t="n">
+        <v>7.375</v>
+      </c>
+      <c r="P29" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D29,F29,G29,I29,K29,M29,O28),0)</f>
+        <v>6</v>
+      </c>
+      <c r="Q29" s="1" t="str">
+        <f aca="false">IF(P29&gt;6,"TEA",IF(P29&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="R29" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="S29" s="1" t="n">
+        <f aca="false">IF(AND(P29&gt;6,R29&gt;6),ROUND((P29+R29)/2,0),MIN(P29,R29))</f>
+        <v>6</v>
+      </c>
+      <c r="T29" s="1" t="str">
+        <f aca="false">IF(S29&gt;6,"TEA",IF(S29&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="U29" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F29" s="1" t="n">
+      <c r="D30" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="G29" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I29" s="1" t="n">
+      <c r="I30" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J30" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O30" s="1" t="n">
         <v>7.75</v>
       </c>
-      <c r="K29" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(D29,E29,F29,G29,H29,I29,J28),0)</f>
-        <v>6</v>
-      </c>
-      <c r="L29" s="1" t="str">
-        <f aca="false">IF(K29&gt;6,"TEA",IF(K29&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+      <c r="P30" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(D30,F30,G30,I30,K30,M30,O29),0)</f>
+        <v>7</v>
+      </c>
+      <c r="Q30" s="1" t="str">
+        <f aca="false">IF(P30&gt;6,"TEA",IF(P30&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="R30" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="S30" s="1" t="n">
+        <f aca="false">IF(AND(P30&gt;6,R30&gt;6),ROUND((P30+R30)/2,0),MIN(P30,R30))</f>
+        <v>7</v>
+      </c>
+      <c r="T30" s="1" t="str">
+        <f aca="false">IF(S30&gt;6,"TEA",IF(S30&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="U30" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G32" s="1" t="n">
+        <f aca="false">(5.6+7+7)/3</f>
+        <v>6.53333333333333</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G33" s="1" t="n">
+        <f aca="false">(2.6+2.1+6.3)/3</f>
+        <v>3.66666666666667</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D3:L5 D6:I29 K6:L29 J6:J23">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+  <conditionalFormatting sqref="D3:T3 D6:N29 O6:O23 P15:Q30 D4:R5 P6:R14 S4:T30">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"TEA"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"TEP"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"TED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J24:J29">
-    <cfRule type="cellIs" priority="8" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+  <conditionalFormatting sqref="O24:O29">
+    <cfRule type="cellIs" priority="8" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="9" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="10" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R15:R30">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>4</formula>
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4126,16 +5166,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4146,7 +5186,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>10</v>
@@ -4163,7 +5203,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>6</v>
@@ -4182,7 +5222,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>3</v>
@@ -4210,7 +5250,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>4</v>
@@ -4227,7 +5267,7 @@
         <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>8</v>
@@ -4244,7 +5284,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>8</v>
@@ -4261,7 +5301,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>10</v>
@@ -4278,7 +5318,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>9</v>
@@ -4295,7 +5335,7 @@
         <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>9</v>
@@ -4312,7 +5352,7 @@
         <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>1</v>
@@ -4343,7 +5383,7 @@
         <v>36</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>10</v>
@@ -4360,7 +5400,7 @@
         <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>10</v>
@@ -4379,7 +5419,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>10</v>
@@ -4387,7 +5427,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>9</v>
@@ -4395,7 +5435,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>6</v>
@@ -4403,7 +5443,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>4</v>
@@ -4411,7 +5451,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>2</v>
@@ -4421,11 +5461,11 @@
       <c r="A21" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>10</v>
@@ -4439,10 +5479,10 @@
         <v>26</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>10</v>
@@ -4456,10 +5496,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>1</v>
@@ -4476,7 +5516,7 @@
         <v>43</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>9</v>
@@ -4493,7 +5533,7 @@
         <v>45</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>10</v>
@@ -4512,7 +5552,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>5</v>
@@ -4526,7 +5566,7 @@
         <v>47</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>8</v>
@@ -4543,7 +5583,7 @@
         <v>49</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>10</v>
@@ -4560,7 +5600,7 @@
         <v>51</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>10</v>
@@ -4577,7 +5617,7 @@
         <v>53</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>3</v>
@@ -4625,7 +5665,7 @@
         <v>58</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>9</v>
@@ -4642,7 +5682,7 @@
         <v>60</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>7</v>
@@ -4659,7 +5699,7 @@
         <v>62</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>8</v>
@@ -4678,7 +5718,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C36" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>8</v>
@@ -4686,7 +5726,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C37" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>3</v>
@@ -4738,16 +5778,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4758,7 +5798,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>9</v>
@@ -4775,7 +5815,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>10</v>
@@ -4794,7 +5834,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>10</v>
@@ -4808,7 +5848,7 @@
         <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>9</v>
@@ -4827,7 +5867,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>8</v>
@@ -4835,7 +5875,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>8</v>
@@ -4843,7 +5883,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>1</v>
@@ -4851,7 +5891,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>1</v>
@@ -4893,7 +5933,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>10</v>
@@ -4910,7 +5950,7 @@
         <v>27</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>2</v>
@@ -4929,7 +5969,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>1</v>
@@ -4957,7 +5997,7 @@
         <v>30</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>8</v>
@@ -4974,7 +6014,7 @@
         <v>32</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>1</v>
@@ -4991,7 +6031,7 @@
         <v>34</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>3</v>
@@ -5033,10 +6073,10 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>10</v>
@@ -5055,7 +6095,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>7</v>
@@ -5063,7 +6103,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>2</v>
@@ -5088,7 +6128,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>1</v>
@@ -5133,7 +6173,7 @@
         <v>47</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>3</v>
@@ -5150,7 +6190,7 @@
         <v>49</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>9</v>
@@ -5167,7 +6207,7 @@
         <v>51</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>6</v>
@@ -5229,7 +6269,7 @@
         <v>58</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>9</v>
@@ -5248,7 +6288,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>3</v>
@@ -5262,7 +6302,7 @@
         <v>60</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>3</v>
@@ -5281,7 +6321,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C37" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>1</v>
@@ -5346,16 +6386,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5366,7 +6406,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>7</v>
@@ -5383,7 +6423,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>9</v>
@@ -5400,7 +6440,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>3</v>
@@ -5417,7 +6457,7 @@
         <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>4</v>
@@ -5434,7 +6474,7 @@
         <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>9</v>
@@ -5453,7 +6493,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>8</v>
@@ -5461,7 +6501,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>8</v>
@@ -5469,7 +6509,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>7</v>
@@ -5477,7 +6517,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>6</v>
@@ -5485,7 +6525,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>3</v>
@@ -5499,7 +6539,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>7</v>
@@ -5516,7 +6556,7 @@
         <v>27</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>7</v>
@@ -5533,7 +6573,7 @@
         <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>7</v>
@@ -5550,7 +6590,7 @@
         <v>30</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>10</v>
@@ -5569,7 +6609,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>10</v>
@@ -5577,7 +6617,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>10</v>
@@ -5585,7 +6625,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>8</v>
@@ -5593,7 +6633,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>7</v>
@@ -5601,7 +6641,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>6</v>
@@ -5609,7 +6649,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>5</v>
@@ -5617,7 +6657,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>5</v>
@@ -5625,7 +6665,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>3</v>
@@ -5639,7 +6679,7 @@
         <v>32</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>4</v>
@@ -5656,7 +6696,7 @@
         <v>34</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>8</v>
@@ -5673,7 +6713,7 @@
         <v>36</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>10</v>
@@ -5692,7 +6732,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>9</v>
@@ -5700,7 +6740,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>9</v>
@@ -5708,7 +6748,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>7</v>
@@ -5722,7 +6762,7 @@
         <v>37</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>9</v>
@@ -5736,10 +6776,10 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>8</v>
@@ -5756,7 +6796,7 @@
         <v>40</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>8</v>
@@ -5770,10 +6810,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>6</v>
@@ -5790,7 +6830,7 @@
         <v>43</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>9</v>
@@ -5809,7 +6849,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>7</v>
@@ -5823,7 +6863,7 @@
         <v>45</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>7</v>
@@ -5840,7 +6880,7 @@
         <v>47</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>8</v>
@@ -5859,7 +6899,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C38" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>6</v>
@@ -5867,7 +6907,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C39" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>6</v>
@@ -5875,7 +6915,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C40" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>5</v>
@@ -5889,7 +6929,7 @@
         <v>49</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>9</v>
@@ -5906,7 +6946,7 @@
         <v>51</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>7</v>
@@ -6008,7 +7048,7 @@
         <v>58</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D50" s="1" t="n">
         <v>7</v>
@@ -6025,7 +7065,7 @@
         <v>60</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D51" s="1" t="n">
         <v>9</v>
@@ -6044,7 +7084,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C52" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D52" s="1" t="n">
         <v>8</v>
@@ -6052,7 +7092,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C53" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D53" s="1" t="n">
         <v>5</v>
@@ -6060,7 +7100,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C54" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D54" s="1" t="n">
         <v>5</v>
@@ -6068,7 +7108,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C55" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D55" s="1" t="n">
         <v>3</v>
@@ -6082,7 +7122,7 @@
         <v>62</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D56" s="1" t="n">
         <v>9</v>
@@ -6136,7 +7176,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6158,7 +7198,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>7</v>
@@ -6205,7 +7245,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>7</v>
@@ -6230,7 +7270,7 @@
         <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>7</v>
@@ -6244,7 +7284,7 @@
         <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>6</v>
@@ -6280,7 +7320,7 @@
         <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>7</v>
@@ -6294,7 +7334,7 @@
         <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>8</v>
@@ -6305,7 +7345,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>1</v>
@@ -6319,7 +7359,7 @@
         <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>6</v>
@@ -6330,7 +7370,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>1</v>
@@ -6344,7 +7384,7 @@
         <v>43</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>7</v>
@@ -6358,7 +7398,7 @@
         <v>45</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>7</v>
@@ -6372,7 +7412,7 @@
         <v>47</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>7</v>
@@ -6386,7 +7426,7 @@
         <v>49</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>10</v>
@@ -6447,7 +7487,7 @@
         <v>58</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>7</v>
@@ -6461,7 +7501,7 @@
         <v>60</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>7</v>
@@ -6475,7 +7515,7 @@
         <v>62</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>6</v>
@@ -6483,7 +7523,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D29" s="1" t="n">
         <f aca="false">COUNTIF(D2:D28,"&gt;0")</f>
@@ -6526,13 +7566,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6543,7 +7583,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>6.25</v>
@@ -6560,7 +7600,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>7</v>
@@ -6577,7 +7617,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>7</v>
@@ -6592,7 +7632,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>5</v>
@@ -6606,7 +7646,7 @@
         <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>4.25</v>
@@ -6623,7 +7663,7 @@
         <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>7.75</v>
@@ -6640,7 +7680,7 @@
         <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>9</v>
@@ -6657,7 +7697,7 @@
         <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>6.5</v>
@@ -6674,7 +7714,7 @@
         <v>28</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>6.5</v>
@@ -6691,7 +7731,7 @@
         <v>30</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>8.5</v>
@@ -6708,7 +7748,7 @@
         <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>5.25</v>
@@ -6725,7 +7765,7 @@
         <v>34</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>5.5</v>
@@ -6742,7 +7782,7 @@
         <v>36</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>10</v>
@@ -6759,7 +7799,7 @@
         <v>37</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>8</v>
@@ -6773,10 +7813,10 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>6.75</v>
@@ -6793,7 +7833,7 @@
         <v>40</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>4.75</v>
@@ -6807,10 +7847,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>5.5</v>
@@ -6838,7 +7878,7 @@
         <v>45</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>5.25</v>
@@ -6855,7 +7895,7 @@
         <v>47</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>7.25</v>
@@ -6872,7 +7912,7 @@
         <v>49</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>9</v>
@@ -6889,7 +7929,7 @@
         <v>51</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>8.25</v>
@@ -6906,7 +7946,7 @@
         <v>53</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>4</v>
@@ -6923,7 +7963,7 @@
         <v>55</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>6.25</v>
@@ -6957,7 +7997,7 @@
         <v>58</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>7.25</v>
@@ -6974,7 +8014,7 @@
         <v>60</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>9</v>
@@ -6989,7 +8029,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>5.75</v>
@@ -7003,7 +8043,7 @@
         <v>62</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>7.75</v>
@@ -7014,7 +8054,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>6.75</v>

--- a/inasistencias-5a-InstrumentalYsistemasElectricos/alumnos-5a-InstrumentalYsistElectricos.xlsx
+++ b/inasistencias-5a-InstrumentalYsistemasElectricos/alumnos-5a-InstrumentalYsistElectricos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="120">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -900,7 +900,7 @@
         <v>46244</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>46223</v>
+        <v>46258</v>
       </c>
       <c r="AC2" s="3" t="n">
         <v>46230</v>
@@ -1044,8 +1044,11 @@
       <c r="Z3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA3" s="4" t="s">
-        <v>13</v>
+      <c r="AA3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB3" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1120,8 +1123,11 @@
       <c r="Z4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA4" s="4" t="s">
-        <v>13</v>
+      <c r="AA4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1202,8 +1208,11 @@
       <c r="Z5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA5" s="4" t="s">
-        <v>13</v>
+      <c r="AA5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1276,8 +1285,11 @@
       <c r="Z6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AA6" s="4" t="s">
-        <v>13</v>
+      <c r="AA6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB6" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1350,8 +1362,11 @@
       <c r="Z7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA7" s="4" t="s">
-        <v>13</v>
+      <c r="AA7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB7" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1424,8 +1439,11 @@
       <c r="Z8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AA8" s="4" t="s">
-        <v>13</v>
+      <c r="AA8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB8" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1498,7 +1516,10 @@
       <c r="Z9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AA9" s="4" t="s">
+      <c r="AA9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB9" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1563,8 +1584,11 @@
       <c r="Z10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AA10" s="4" t="s">
-        <v>13</v>
+      <c r="AA10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB10" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1637,8 +1661,11 @@
       <c r="Z11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AA11" s="4" t="s">
-        <v>13</v>
+      <c r="AA11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB11" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1711,8 +1738,11 @@
       <c r="Z12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA12" s="4" t="s">
-        <v>13</v>
+      <c r="AA12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB12" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1785,8 +1815,11 @@
       <c r="Z13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA13" s="4" t="s">
-        <v>13</v>
+      <c r="AA13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB13" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1859,8 +1892,11 @@
       <c r="Z14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA14" s="4" t="s">
-        <v>13</v>
+      <c r="AA14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB14" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1934,8 +1970,11 @@
       <c r="Z15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA15" s="4" t="s">
-        <v>13</v>
+      <c r="AA15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB15" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="AKW15" s="1"/>
       <c r="AKX15" s="1"/>
@@ -2095,8 +2134,11 @@
       <c r="Z16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AA16" s="4" t="s">
-        <v>13</v>
+      <c r="AA16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB16" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2160,8 +2202,11 @@
       <c r="Z17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AA17" s="4" t="s">
-        <v>13</v>
+      <c r="AA17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB17" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2235,7 +2280,10 @@
       <c r="Z18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA18" s="4" t="s">
+      <c r="AA18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB18" s="2" t="s">
         <v>13</v>
       </c>
       <c r="AKW18" s="1"/>
@@ -2388,7 +2436,10 @@
       <c r="Z19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AA19" s="4" t="s">
+      <c r="AA19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB19" s="6" t="s">
         <v>13</v>
       </c>
       <c r="AKW19" s="5"/>
@@ -2546,8 +2597,11 @@
       <c r="Z20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AA20" s="4" t="s">
-        <v>13</v>
+      <c r="AA20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2623,8 +2677,11 @@
       <c r="Z21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA21" s="4" t="s">
-        <v>13</v>
+      <c r="AA21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB21" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2700,8 +2757,11 @@
       <c r="Z22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA22" s="4" t="s">
-        <v>13</v>
+      <c r="AA22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB22" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2774,8 +2834,11 @@
       <c r="Z23" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA23" s="4" t="s">
-        <v>13</v>
+      <c r="AA23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB23" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2849,8 +2912,11 @@
       <c r="Z24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AA24" s="4" t="s">
-        <v>13</v>
+      <c r="AA24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB24" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="AKW24" s="1"/>
       <c r="AKX24" s="1"/>
@@ -3007,7 +3073,10 @@
       <c r="Z25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AA25" s="4" t="s">
+      <c r="AA25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB25" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3081,8 +3150,11 @@
       <c r="Z26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA26" s="4" t="s">
-        <v>13</v>
+      <c r="AA26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB26" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3158,7 +3230,10 @@
       <c r="Z27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA27" s="4" t="s">
+      <c r="AA27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB27" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3227,8 +3302,11 @@
       <c r="Z28" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA28" s="4" t="s">
-        <v>13</v>
+      <c r="AA28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB28" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="29" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3291,8 +3369,11 @@
       <c r="Z29" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AA29" s="4" t="s">
-        <v>13</v>
+      <c r="AA29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB29" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="30" s="5" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3345,8 +3426,11 @@
       <c r="Z30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AA30" s="4" t="s">
-        <v>13</v>
+      <c r="AA30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB30" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3401,6 +3485,10 @@
       <c r="AA31" s="2" t="n">
         <f aca="false">COUNTIF(AA3:AA30,"P")</f>
         <v>1</v>
+      </c>
+      <c r="AB31" s="2" t="n">
+        <f aca="false">COUNTIF(AB3:AB30,"P")</f>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/inasistencias-5a-InstrumentalYsistemasElectricos/alumnos-5a-InstrumentalYsistElectricos.xlsx
+++ b/inasistencias-5a-InstrumentalYsistemasElectricos/alumnos-5a-InstrumentalYsistElectricos.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="120">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -805,8 +805,8 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.79"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="35.71"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="20" min="5" style="1" width="8.86"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="21" min="5" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="28" min="22" style="0" width="8.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="985" min="985" style="1" width="9.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16346" style="1" width="10.58"/>
   </cols>
@@ -903,13 +903,13 @@
         <v>46258</v>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>46230</v>
+        <v>46265</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="AF2" s="3" t="n">
         <v>46251</v>
@@ -1047,7 +1047,16 @@
       <c r="AA3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB3" s="4" t="s">
+      <c r="AB3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE3" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1126,7 +1135,16 @@
       <c r="AA4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB4" s="4" t="s">
+      <c r="AB4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE4" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1211,7 +1229,16 @@
       <c r="AA5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB5" s="4" t="s">
+      <c r="AB5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE5" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1288,7 +1315,16 @@
       <c r="AA6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB6" s="4" t="s">
+      <c r="AB6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE6" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1365,7 +1401,16 @@
       <c r="AA7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB7" s="4" t="s">
+      <c r="AB7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE7" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1442,7 +1487,16 @@
       <c r="AA8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB8" s="4" t="s">
+      <c r="AB8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE8" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1519,8 +1573,17 @@
       <c r="AA9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB9" s="4" t="s">
-        <v>13</v>
+      <c r="AB9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE9" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1590,6 +1653,15 @@
       <c r="AB10" s="5" t="s">
         <v>12</v>
       </c>
+      <c r="AC10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE10" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -1664,7 +1736,16 @@
       <c r="AA11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB11" s="4" t="s">
+      <c r="AB11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE11" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1741,7 +1822,16 @@
       <c r="AA12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB12" s="4" t="s">
+      <c r="AB12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE12" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1818,7 +1908,16 @@
       <c r="AA13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB13" s="4" t="s">
+      <c r="AB13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE13" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1895,7 +1994,16 @@
       <c r="AA14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB14" s="4" t="s">
+      <c r="AB14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE14" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1974,6 +2082,15 @@
         <v>13</v>
       </c>
       <c r="AB15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="AKW15" s="1"/>
@@ -2140,6 +2257,15 @@
       <c r="AB16" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AC16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE16" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="17" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
@@ -2208,6 +2334,15 @@
       <c r="AB17" s="5" t="s">
         <v>12</v>
       </c>
+      <c r="AC17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE17" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="18" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
@@ -2285,6 +2420,15 @@
       </c>
       <c r="AB18" s="2" t="s">
         <v>13</v>
+      </c>
+      <c r="AC18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE18" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="AKW18" s="1"/>
       <c r="AKX18" s="1"/>
@@ -2442,6 +2586,15 @@
       <c r="AB19" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="AC19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE19" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="AKW19" s="5"/>
       <c r="AKX19" s="5"/>
       <c r="AKY19" s="5"/>
@@ -2603,6 +2756,15 @@
       <c r="AB20" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AC20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -2680,7 +2842,16 @@
       <c r="AA21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB21" s="4" t="s">
+      <c r="AB21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE21" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2760,7 +2931,16 @@
       <c r="AA22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB22" s="4" t="s">
+      <c r="AB22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE22" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2837,7 +3017,16 @@
       <c r="AA23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB23" s="4" t="s">
+      <c r="AB23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE23" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2916,6 +3105,15 @@
         <v>13</v>
       </c>
       <c r="AB24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="AKW24" s="1"/>
@@ -3076,7 +3274,16 @@
       <c r="AA25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB25" s="4" t="s">
+      <c r="AB25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE25" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3153,7 +3360,16 @@
       <c r="AA26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB26" s="4" t="s">
+      <c r="AB26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE26" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3233,7 +3449,16 @@
       <c r="AA27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AB27" s="4" t="s">
+      <c r="AB27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE27" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3305,7 +3530,16 @@
       <c r="AA28" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AB28" s="4" t="s">
+      <c r="AB28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE28" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3373,6 +3607,15 @@
         <v>13</v>
       </c>
       <c r="AB29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE29" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3431,6 +3674,15 @@
       </c>
       <c r="AB30" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="AC30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE30" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3489,6 +3741,18 @@
       <c r="AB31" s="2" t="n">
         <f aca="false">COUNTIF(AB3:AB30,"P")</f>
         <v>24</v>
+      </c>
+      <c r="AC31" s="2" t="n">
+        <f aca="false">COUNTIF(AC3:AC30,"P")</f>
+        <v>23</v>
+      </c>
+      <c r="AD31" s="2" t="n">
+        <f aca="false">COUNTIF(AD3:AD30,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="AE31" s="2" t="n">
+        <f aca="false">COUNTIF(AE3:AE30,"P")</f>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
